--- a/Assets/Data/Excel/Artifacts.xlsx
+++ b/Assets/Data/Excel/Artifacts.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Artifacts" sheetId="1" r:id="rId1"/>
     <sheet name="UnitStatEffects" sheetId="2" r:id="rId2"/>
     <sheet name="CurrencyEffects" sheetId="3" r:id="rId3"/>
+    <sheet name="ConsumableSlotEffects" sheetId="4" r:id="rIdConsumableSlots"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1186,9 +1187,33 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/consumableSlots.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ArtifactId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AdditionalSlots</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1198,173 +1223,1055 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ArtifactId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서리 묻은 족쇄</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적 전체 이동속도 5% 감소</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마력의 외투</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마법사 클래스 방어력 3 증가</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박동의 북</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 공격속도 3% 증가</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승부사의 주사위</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 치명타 피해 배율 15%p 증가</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">황동 톱니바퀴</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건물 골드 생산 보상 지급 시마다 기본 지급량 3 추가</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">망자의 봉헌함</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run 종료 혈석 정산의 기본 지급량 15 추가</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숲지기의 망토</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁수 클래스 최대 체력 8% 증가</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">침묵의 검약</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 기본 공격 배율 80% 증가. 스킬 배율 40% 감소(현재 스킬 배율을 사용하는 회복량에도 적용)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythic</t>
+        </is>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추격자의 나침반</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검사 클래스 이동속도와 탐지 범위 15% 증가</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병사의 휘장</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 공격력 5% 증가</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생명의 씨앗</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 최대 체력 5% 증가</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">낡은 철갑</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전사 클래스 방어력 3 증가</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가벼운 장화</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 이동속도 5% 증가</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정찰병의 망원경</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 탐지 범위 15% 증가</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수련자의 장갑</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검사 클래스 기본 공격 배율 8% 증가</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재생의 붕대</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 받는 회복량 배율 8% 증가</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날카로운 화살촉</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁수 클래스 치명타 확률 2%p 증가</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">행운의 동전</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웨이브 클리어 골드 지급량 10 추가</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 풍차</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건물 골드 생산량 5% 증가</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수호의 방패</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전사 클래스 받는 피해 배율 8% 감소</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결투가의 손목띠</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검사 클래스 공격속도 12% 증가</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비전의 수정</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마법사 클래스 스킬 배율 15% 증가</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모래시계 조각</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마법사 클래스 쿨다운 감소율 5%p 증가</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">관통의 화살촉</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁수 클래스 방어력 무시 비율 8%p 증가</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흡혈의 송곳니</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검사 클래스 흡혈 비율 3%p 증가</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치유자의 성물</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 주는 회복량 배율 15% 증가</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처형자의 표식</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁수 클래스 치명타 피해 배율 20%p 증가</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전쟁의 인장</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 피해 배율 8% 증가</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상인의 인장</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웨이브 클리어 골드 지급량 15% 증가</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불굴의 군기</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 최대 체력 20%, 공격력 15% 증가</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E31">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10">
-        <v>99</v>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">철벽의 심장</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WA_T1_전사 타입 방어력 20% 증가, 받는 피해 배율 10% 감소</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검성의 유산</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SW_T1_검사 타입 기본 공격 배율 25%, 흡혈 비율 5%p 증가</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명사수의 증표</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR_T1_궁수 타입 방어력 무시 비율 15%p, 치명타 피해 배율 30%p 증가</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대마법사의 서</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG_T1_마법사 타입 스킬 배율 25%, 쿨다운 감소율 8%p 증가</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쇠락의 왕관</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적 전체 공격력 10%, 방어력 15% 감소</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">황금 기관</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건물 골드 생산량 30% 증가</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">혈석의 성배</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run 종료 혈석 정산 지급량 30% 증가</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legendary</t>
+        </is>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">광전사의 맹약</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 공격력 60%, 공격속도 25% 증가. 최대 체력 30% 감소</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythic</t>
+        </is>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">탐욕의 심장</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웨이브 클리어 골드 지급량 80% 증가. 적 전체 공격력과 최대 체력 25% 증가</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythic</t>
+        </is>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유리별의 핵</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마법사 클래스 스킬 배율 70%, 쿨다운 감소율 15%p 증가. 최대 체력 40% 감소</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythic</t>
+        </is>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피의 왕관</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아군 전체 피해 배율 40%, 흡혈 비율 10%p 증가. 받는 피해 배율 30% 증가</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythic</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1376,266 +2283,2512 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" t="s">
-        <v>46</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ArtifactId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TargetTeam</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ApplyType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AllyClass</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>AllyType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>EnemyClass</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EnemyType</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ModifierType</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MoveSpeed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="J2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>46</v>
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defense</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackSpeed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="J4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J5">
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archer</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_008</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackMultiplier</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swordsman</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MoveSpeed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swordsman</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DetectionRange</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackPower</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warrior</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defense</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J13">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MoveSpeed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DetectionRange</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swordsman</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackMultiplier</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J16">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HealingTakenMultiplier</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J17">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalChance</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J18">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_020</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warrior</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageTakenMultiplier</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J19">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_021</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swordsman</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackSpeed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J20">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CooldownReduction</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archer</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DefenseIgnore</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J23">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swordsman</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LifeSteal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HealingMultiplier</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archer</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J26">
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_028</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J27">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_030</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J28">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackPower</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J29">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_031</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WA_T1_전사</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defense</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J30">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_031</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WA_T1_전사</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageTakenMultiplier</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J31">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_032</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SW_T1_검사</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackMultiplier</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SW_T1_검사</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LifeSteal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR_T1_궁수</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DefenseIgnore</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J34">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_033</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR_T1_궁수</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J35">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_034</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG_T1_마법사</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J36">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_034</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG_T1_마법사</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CooldownReduction</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J37">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_035</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackPower</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J38">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defense</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J39">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_038</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackPower</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J40">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_038</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackSpeed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J41">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J42">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_039</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackPower</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J43">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_039</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J44">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_040</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillDamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J45">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_040</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CooldownReduction</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J46">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_040</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Class</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mage</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J47">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_041</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageMultiplier</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J48">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_041</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LifeSteal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="J49">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_041</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ally</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageTakenMultiplier</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J50">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1647,78 +4800,237 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ArtifactId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RewardType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ModifierType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_005</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_006</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloodstone</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RunSettlement</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_018</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaveReward</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4">
-        <v>0.2</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_029</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaveReward</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_036</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_037</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloodstone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RunSettlement</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artifact_039</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gold</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaveReward</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/Artifacts.xlsx
+++ b/Assets/Data/Excel/Artifacts.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run 종료 혈석 정산의 기본 지급량 15 추가</t>
+          <t>웨이브 클리어 보석 지급량 1 추가</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">혈석의 성배</t>
+          <t>보석의 성배</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run 종료 혈석 정산 지급량 30% 증가</t>
+          <t>웨이브 클리어 보석 지급량 10% 증가</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloodstone</t>
+          <t>Gem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RunSettlement</t>
+          <t>WaveReward</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloodstone</t>
+          <t>Gem</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RunSettlement</t>
+          <t>WaveReward</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">

--- a/Assets/Data/Excel/Artifacts.xlsx
+++ b/Assets/Data/Excel/Artifacts.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>적 전체 이동속도 5% 감소</t>
+          <t>적 전체의 이동속도가 5% 감소</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>마법사 클래스 방어력 3 증가</t>
+          <t>아군 마법사 클래스의 방어력이 3 증가</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 공격속도 3% 증가</t>
+          <t>아군 전체의 공격속도가 3% 증가</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 치명타 피해 배율 15%p 증가</t>
+          <t>아군 전체의 치명타 피해 배율이 15% 증가</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>건물 골드 생산 보상 지급 시마다 기본 지급량 3 추가</t>
+          <t>건물의 골드 생산 보상이 지급될 때마다 기본 지급량이 3 증가</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>웨이브 클리어 보석 지급량 1 추가</t>
+          <t>웨이브 클리어 시 지급되는 보석이 1개 증가</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>궁수 클래스 최대 체력 8% 증가</t>
+          <t>아군 궁수 클래스의 최대 체력이 8% 증가</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 기본 공격 배율 80% 증가. 스킬 배율 40% 감소(현재 스킬 배율을 사용하는 회복량에도 적용)</t>
+          <t>아군 전체의 기본 공격 배율이 80% 증가하고 스킬 배율이 40% 감소. 스킬 배율을 사용하는 회복량에도 적용</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>검사 클래스 이동속도와 탐지 범위 15% 증가</t>
+          <t>아군 검사 클래스의 이동속도와 탐지 범위가 15% 증가</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 공격력 5% 증가</t>
+          <t>아군 전체의 공격력이 5% 증가</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 최대 체력 5% 증가</t>
+          <t>아군 전체의 최대 체력이 5% 증가</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>전사 클래스 방어력 3 증가</t>
+          <t>아군 전사 클래스의 방어력이 3 증가</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 이동속도 5% 증가</t>
+          <t>아군 전체의 이동속도가 5% 증가</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 탐지 범위 15% 증가</t>
+          <t>아군 전체의 탐지 범위가 15% 증가</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>검사 클래스 기본 공격 배율 8% 증가</t>
+          <t>아군 검사 클래스의 기본 공격 배율이 8% 증가</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 받는 회복량 배율 8% 증가</t>
+          <t>아군 전체가 받는 회복량 배율이 8% 증가</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>궁수 클래스 치명타 확률 2%p 증가</t>
+          <t>아군 궁수 클래스의 치명타 확률이 2% 증가</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>웨이브 클리어 골드 지급량 10 추가</t>
+          <t>웨이브 클리어 시 지급되는 골드가 10 증가</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>건물 골드 생산량 5% 증가</t>
+          <t>건물의 골드 생산량이 5% 증가</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>전사 클래스 받는 피해 배율 8% 감소</t>
+          <t>아군 전사 클래스가 받는 피해 배율이 8% 감소</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>검사 클래스 공격속도 12% 증가</t>
+          <t>아군 검사 클래스의 공격속도가 12% 증가</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>마법사 클래스 스킬 배율 15% 증가</t>
+          <t>아군 마법사 클래스의 스킬 배율이 15% 증가</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>마법사 클래스 쿨다운 감소율 5%p 증가</t>
+          <t>아군 마법사 클래스의 쿨다운 감소율이 5% 증가</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>궁수 클래스 방어력 무시 비율 8%p 증가</t>
+          <t>아군 궁수 클래스의 방어력 무시 비율이 8% 증가</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>검사 클래스 흡혈 비율 3%p 증가</t>
+          <t>아군 검사 클래스의 흡혈 비율이 3% 증가</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 주는 회복량 배율 15% 증가</t>
+          <t>아군 전체가 주는 회복량 배율이 15% 증가</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>궁수 클래스 치명타 피해 배율 20%p 증가</t>
+          <t>아군 궁수 클래스의 치명타 피해 배율이 20% 증가</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 피해 배율 8% 증가</t>
+          <t>아군 전체가 주는 피해 배율이 8% 증가</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>웨이브 클리어 골드 지급량 15% 증가</t>
+          <t>웨이브 클리어 시 지급되는 골드가 15% 증가</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 최대 체력 20%, 공격력 15% 증가</t>
+          <t>아군 전체의 최대 체력이 20%, 공격력이 15% 증가</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>아군 전사(1티어) 방어력 50% 증가, 받는 피해 배율 20% 감소</t>
+          <t>아군 전사(1티어)의 방어력이 50% 증가하고 받는 피해 배율이 20% 감소</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>아군 검사(1티어) 기본 공격 배율 50%, 흡혈 비율 8%p 증가</t>
+          <t>아군 검사(1티어)의 기본 공격 배율이 50%, 흡혈 비율이 8% 증가</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>아군 궁수(1티어) 방어력 무시 비율 25%p, 치명타 피해 배율 50%p 증가</t>
+          <t>아군 궁수(1티어)의 방어력 무시 비율이 25%, 치명타 피해 배율이 50% 증가</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>아군 마법사(1티어) 스킬 배율 50%, 쿨다운 감소율 12%p 증가</t>
+          <t>아군 마법사(1티어)의 스킬 배율이 50%, 쿨다운 감소율이 12% 증가</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>적 전체 공격력 10%, 방어력 15% 감소</t>
+          <t>적 전체의 공격력이 10%, 방어력이 15% 감소</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>건물 골드 생산량 30% 증가</t>
+          <t>건물의 골드 생산량이 30% 증가</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>보석이 포함된 웨이브 클리어 보상의 보석 지급량 2 추가</t>
+          <t>웨이브 클리어 보상에 보석이 포함되어 있으면 지급되는 보석이 2개 증가</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 공격력 45%, 공격속도 20% 증가. 최대 체력 30% 감소</t>
+          <t>아군 전체의 공격력이 45%, 공격속도가 20% 증가하고 최대 체력이 30% 감소</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>웨이브 클리어 골드 지급량 80% 증가. 적 전체 공격력과 최대 체력 25% 증가</t>
+          <t>웨이브 클리어 시 지급되는 골드가 80% 증가하고 적 전체의 공격력과 최대 체력이 25% 증가</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>마법사 클래스 스킬 배율 70%, 쿨다운 감소율 15%p 증가. 최대 체력 40% 감소</t>
+          <t>아군 마법사 클래스의 스킬 배율이 70%, 쿨다운 감소율이 15% 증가하고 최대 체력이 40% 감소</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>아군 전체 피해 배율 40%, 흡혈 비율 10%p 증가. 받는 피해 배율 30% 증가</t>
+          <t>아군 전체가 주는 피해 배율이 40%, 흡혈 비율이 10% 증가하고 받는 피해 배율이 30% 증가</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 아군 전체: 체력이 처음 25% 이하가 되면 자신의 최대 체력 15%를 회복한다. 유닛당 1회.</t>
+          <t>아군 유닛의 체력이 처음 25% 이하가 되면 자신의 최대 체력의 15%만큼 회복. 유닛마다 1회 발동</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 마법사 클래스: 액티브 완료 시 자신의 최대 체력 5% 보호막을 획득한다.</t>
+          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신의 최대 체력의 5%만큼 보호막 획득</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 반경 2의 적이 3명 이상인 동안 공격속도 +20%. 0.5초마다 확인한다.</t>
+          <t>아군 전사 클래스는 자신 주변 반경 2에 적이 3명 이상 있으면 공격속도가 20% 증가. 조건은 0.5초마다 확인</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 시프: 중독된 대상에게 주는 피해 +25%.</t>
+          <t>시프가 중독된 대상에게 주는 피해가 25% 증가</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 검사 클래스: 반경 2의 적이 정확히 1명인 동안 주는 피해 +20%. 0.5초마다 확인한다.</t>
+          <t>아군 검사 클래스는 자신 주변 반경 2에 적이 정확히 1명 있으면 주는 피해가 20% 증가. 조건은 0.5초마다 확인</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 액티브 완료 시 4초간 이동속도 +15%. 재발동 시 시간만 갱신한다.</t>
+          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 4초 동안 이동속도가 15% 증가. 다시 발동하면 지속시간만 갱신</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 액티브 완료 시 반경 16의 가까운 적 최대 3명에게 각각 공격력 50% 추가 물리 투사체를 발사한다.</t>
+          <t>아군 궁수 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 16의 가까운 적 최대 3명에게 각각 공격력의 50%에 해당하는 물리 피해를 주는 추가 투사체 발사</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 체력 80% 이상인 동안 공격력 +15%.</t>
+          <t>아군 궁수 클래스는 체력이 80% 이상이면 공격력이 15% 증가</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 아군 1티어: 체력 50% 이하인 동안 공격력 +25%.</t>
+          <t>아군 1티어 유닛은 체력이 50% 이하이면 공격력이 25% 증가</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 마법사 클래스: 액티브 완료 시 반경 8의 적 최대 3명에게 4초간 이동속도 -30%. 재발동 시 시간만 갱신한다.</t>
+          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 8의 적 최대 3명의 이동속도가 4초 동안 30% 감소. 다시 발동하면 지속시간만 갱신</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 광신도 클래스: 액티브 완료 시 반경 3의 다른 아군 최대 3명에게 시전자 최대 체력 8% 보호막을 부여한다.</t>
+          <t>아군 광신도 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 3의 다른 아군 최대 3명에게 자신의 최대 체력의 8%만큼 보호막 부여</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 광신도 클래스: 반경 3 안에 다른 아군이 1명 이상인 동안 주는 회복량과 보호막량 +20%.</t>
+          <t>아군 광신도 클래스는 자신 주변 반경 3에 다른 아군이 1명 이상 있으면 주는 회복량과 보호막량이 20% 증가</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 아군 1티어: 생성 시 자신의 최대 체력 10% 보호막을 획득한다.</t>
+          <t>아군 1티어 유닛이 생성되면 자신의 최대 체력의 10%만큼 보호막 획득</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 마법사 클래스: 액티브 완료 시 자신의 최대 체력 2%를 회복한다.</t>
+          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신의 최대 체력의 2%만큼 회복</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 적 처치 시 4초간 공격력 +10%. 재발동 시 시간만 갱신한다.</t>
+          <t>아군 궁수 클래스가 적을 처치하면 4초 동안 공격력이 10% 증가. 다시 발동하면 지속시간만 갱신</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 액티브 완료 시 5초간 받는 피해 20% 감소. 재발동 시 시간만 갱신한다.</t>
+          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 5초 동안 받는 피해가 20% 감소. 다시 발동하면 지속시간만 갱신</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 검사 클래스: 액티브 완료 시 반경 5의 가까운 적 최대 2명에게 각각 공격력 75% 추가 물리 공격.</t>
+          <t>아군 검사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 5의 가까운 적 최대 2명에게 각각 공격력의 75%에 해당하는 추가 물리 피해</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 광전사: 체력 60% 이하인 동안 받는 회복량과 보호막량 +50%.</t>
+          <t>광전사는 체력이 60% 이하이면 받는 회복량과 보호막량이 50% 증가</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 저격수: 체력이 처음 40% 이하가 되면 자신의 최대 체력 40% 보호막을 획득한다. 유닛당 1회.</t>
+          <t>저격수의 체력이 처음 40% 이하가 되면 자신의 최대 체력의 40%만큼 보호막 획득. 유닛마다 1회 발동</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 아군 1티어: 첫 액티브 스킬 시작 시 20초간 공격속도 +40%. 유닛당 1회.</t>
+          <t>아군 1티어 유닛이 처음 액티브 스킬 사용을 시작하면 20초 동안 공격속도가 40% 증가. 유닛마다 1회 발동</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 체력 50% 이하인 동안 공격속도 +75%. 체력과 관계없이 받는 피해 +20%.</t>
+          <t>아군 전사 클래스는 체력이 50% 이하이면 공격속도가 75% 증가. 체력과 관계없이 받는 피해가 20% 증가</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 검사 클래스: 액티브 완료 시 5초간 공격속도 +60%. 재발동 시 시간만 갱신. 항상 받는 회복량과 보호막량 -30%.</t>
+          <t>아군 검사 클래스가 액티브 스킬 사용을 완료하면 5초 동안 공격속도가 60% 증가. 다시 발동하면 지속시간만 갱신. 받는 회복량과 보호막량은 항상 30% 감소</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 액티브 완료 시 반경 16의 가까운 적 최대 4명에게 각각 공격력 100% 추가 물리 투사체. 항상 공격력 -10%.</t>
+          <t>아군 궁수 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 16의 가까운 적 최대 4명에게 각각 공격력의 100%에 해당하는 물리 피해를 주는 추가 투사체 발사. 공격력은 항상 10% 감소</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 광신도 클래스: 6초마다 반경 3의 다른 아군 최대 3명을 각각 시전자 최대 체력 15%만큼 회복한다. 시전자 최대 체력 -20%.</t>
+          <t>아군 광신도 클래스가 6초마다 자신 주변 반경 3의 다른 아군 최대 3명의 체력을 각각 자신의 최대 체력의 15%만큼 회복. 자신의 최대 체력은 20% 감소</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 아군 전체: 6초마다 체력이 50% 이하이면 자신을 최대 체력의 2%만큼 회복한다.</t>
+          <t>아군 유닛은 6초마다 자신의 체력이 50% 이하이면 최대 체력의 2%만큼 회복</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 검사 클래스: 적 처치 시 3초 동안 이동속도 +12%. 재발동 시 지속시간 갱신.</t>
+          <t>아군 검사 클래스가 적을 처치하면 3초 동안 이동속도가 12% 증가. 다시 발동하면 지속시간 갱신</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 장궁수: 스킬 사용 완료 시 자신 주변 반경 6의 적 최대 2명에게 0.7초 속박.</t>
+          <t>장궁수가 액티브 스킬 사용을 완료하면 자신 주변 반경 6의 적 최대 2명을 0.7초 동안 속박</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 검사 클래스: 피해를 줄 때마다 4초 동안 공격력 +3%, 최대 5중첩. 재발동 시 지속시간 갱신.</t>
+          <t>아군 검사 클래스가 피해를 줄 때마다 4초 동안 공격력이 3% 증가하며 최대 5회 중첩. 다시 발동하면 지속시간 갱신</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 반경 3에 다른 아군이 없으면 공격력 +18%.</t>
+          <t>아군 궁수 클래스는 자신 주변 반경 3에 다른 아군이 없으면 공격력이 18% 증가</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 화염술사: 화상 상태의 적에게 주는 피해 +20%.</t>
+          <t>화염술사가 화상 상태의 적에게 주는 피해가 20% 증가</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 철갑전사: 피해를 받을 때마다 4초 동안 방어력 +5%, 최대 4중첩. 재발동 시 지속시간 갱신.</t>
+          <t>철갑전사가 피해를 받을 때마다 4초 동안 방어력이 5% 증가하며 최대 4회 중첩. 다시 발동하면 지속시간 갱신</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 스킬 사용 완료 시 자신 주변 반경 2.5의 적 최대 3명에게 0.4초 기절.</t>
+          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 2.5의 적 최대 3명을 0.4초 동안 기절시킴</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 마법사 클래스: 스킬 사용 완료 시 자신 주변 반경 5의 적 최대 2명에게 1초 침묵.</t>
+          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 5의 적 최대 2명을 1초 동안 침묵시킴</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 빙결술사: 7초마다 자신 주변 반경 5의 적 최대 2명에게 0.6초 동결.</t>
+          <t>빙결술사가 7초마다 자신 주변 반경 5의 적 최대 2명을 0.6초 동안 동결시킴</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 전사 클래스: 피해를 줄 때마다 공격력 +5%, 최대 10중첩. 유닛이 유지되는 동안 지속. 받는 피해 +25%.</t>
+          <t>아군 전사 클래스가 피해를 줄 때마다 공격력이 5% 증가하며 최대 10회 중첩. 유닛이 유지되는 동안 지속되며 받는 피해가 25% 증가</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>획득 이후 생성되는 궁수 클래스: 적 처치 시 처치 위치 반경 4의 적 최대 2명에게 공격력 60%의 물리 피해 투사체 발사. 공격력 -15%.</t>
+          <t>아군 궁수 클래스가 적을 처치하면 처치 위치 주변 반경 4의 적 최대 2명에게 공격력의 60%에 해당하는 물리 피해를 주는 투사체 발사. 공격력은 15% 감소</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">

--- a/Assets/Data/Excel/Artifacts.xlsx
+++ b/Assets/Data/Excel/Artifacts.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스의 방어력이 3 증가</t>
+          <t xml:space="preserve">마법사 계열 아군의 방어력이 3 증가</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>건물의 골드 생산 보상이 지급될 때마다 기본 지급량이 3 증가</t>
+          <t xml:space="preserve">건물에서 골드를 생산할 때마다 기본 생산량이 3 증가</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스의 최대 체력이 8% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군의 최대 체력이 8% 증가</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -746,7 +746,8 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>아군 전체의 기본 공격 배율이 80% 증가하고 스킬 배율이 40% 감소. 스킬 배율을 사용하는 회복량에도 적용</t>
+          <t xml:space="preserve">아군 전체의 기본 공격 배율이 80% 증가하고 스킬 배율이 40% 감소
+스킬 배율에 영향을 받는 회복량도 함께 감소</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -771,7 +772,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>아군 검사 클래스의 이동속도와 탐지 범위가 15% 증가</t>
+          <t xml:space="preserve">검사 계열 아군의 이동속도와 탐지 범위가 15% 증가</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -846,7 +847,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>아군 전사 클래스의 방어력이 3 증가</t>
+          <t xml:space="preserve">전사 계열 아군의 방어력이 3 증가</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -921,7 +922,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>아군 검사 클래스의 기본 공격 배율이 8% 증가</t>
+          <t xml:space="preserve">검사 계열 아군의 기본 공격 배율이 8% 증가</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -971,7 +972,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스의 치명타 확률이 2% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군의 치명타 확률이 2% 증가</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -1046,7 +1047,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>아군 전사 클래스가 받는 피해 배율이 8% 감소</t>
+          <t xml:space="preserve">전사 계열 아군이 받는 피해 배율이 8% 감소</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -1071,7 +1072,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>아군 검사 클래스의 공격속도가 12% 증가</t>
+          <t xml:space="preserve">검사 계열 아군의 공격속도가 12% 증가</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -1096,7 +1097,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스의 스킬 배율이 15% 증가</t>
+          <t xml:space="preserve">마법사 계열 아군의 스킬 배율이 15% 증가</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -1121,7 +1122,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스의 쿨다운 감소율이 5% 증가</t>
+          <t xml:space="preserve">마법사 계열 아군의 쿨다운 감소율이 5% 증가</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -1146,7 +1147,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스의 방어력 무시 비율이 8% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군의 방어력 무시 비율이 8% 증가</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -1171,7 +1172,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>아군 검사 클래스의 흡혈 비율이 3% 증가</t>
+          <t xml:space="preserve">검사 계열 아군의 흡혈 비율이 3% 증가</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -1221,7 +1222,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스의 치명타 피해 배율이 20% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군의 치명타 피해 배율이 20% 증가</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -1546,7 +1547,7 @@
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스의 스킬 배율이 70%, 쿨다운 감소율이 15% 증가하고 최대 체력이 40% 감소</t>
+          <t xml:space="preserve">마법사 계열 아군의 스킬 배율이 70%, 쿨다운 감소율이 15% 증가하고 최대 체력이 40% 감소</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -1596,7 +1597,8 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>아군 유닛의 체력이 처음 25% 이하가 되면 자신의 최대 체력의 15%만큼 회복. 유닛마다 1회 발동</t>
+          <t xml:space="preserve">아군 유닛의 체력이 처음 25% 이하로 떨어지면 자신의 최대 체력의 15%만큼 회복
+유닛당 1회 발동</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -1621,7 +1623,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신의 최대 체력의 5%만큼 보호막 획득</t>
+          <t xml:space="preserve">마법사 계열 아군이 액티브 스킬 사용을 마치면 자신의 최대 체력의 5%만큼 보호막 획득</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -1646,7 +1648,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스는 자신 주변 반경 2에 적이 3명 이상 있으면 공격속도가 20% 증가. 조건은 0.5초마다 확인</t>
+          <t xml:space="preserve">전사 계열 아군은 주변 반경 2 안에 적이 3명 이상 있으면 공격속도가 20% 증가
+0.5초마다 갱신</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -1696,7 +1699,8 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>아군 검사 클래스는 자신 주변 반경 2에 적이 정확히 1명 있으면 주는 피해가 20% 증가. 조건은 0.5초마다 확인</t>
+          <t xml:space="preserve">검사 계열 아군은 주변 반경 2 안에 적이 1명만 있으면 주는 피해가 20% 증가
+0.5초마다 갱신</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -1721,7 +1725,8 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 4초 동안 이동속도가 15% 증가. 다시 발동하면 지속시간만 갱신</t>
+          <t xml:space="preserve">전사 계열 아군이 액티브 스킬 사용을 마치면 4초 동안 이동속도가 15% 증가
+중첩되지 않으며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -1746,7 +1751,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 16의 가까운 적 최대 3명에게 각각 공격력의 50%에 해당하는 물리 피해를 주는 추가 투사체 발사</t>
+          <t xml:space="preserve">궁수 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 16 안의 가까운 적 최대 3명에게 추가 투사체를 발사해 각각 공격력의 50%만큼 물리 피해를 줌</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -1771,7 +1776,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스는 체력이 80% 이상이면 공격력이 15% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군은 체력이 80% 이상일 때 공격력이 15% 증가</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -1796,7 +1801,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>아군 1티어 유닛은 체력이 50% 이하이면 공격력이 25% 증가</t>
+          <t xml:space="preserve">아군 1티어 유닛은 체력이 50% 이하일 때 공격력이 25% 증가</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -1821,7 +1826,8 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 8의 적 최대 3명의 이동속도가 4초 동안 30% 감소. 다시 발동하면 지속시간만 갱신</t>
+          <t xml:space="preserve">마법사 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 8 안의 적 최대 3명의 이동속도를 4초 동안 30% 감소시킴
+중첩되지 않으며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -1846,7 +1852,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>아군 광신도 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 3의 다른 아군 최대 3명에게 자신의 최대 체력의 8%만큼 보호막 부여</t>
+          <t xml:space="preserve">광신도 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 3 안의 다른 아군 최대 3명에게 자신의 최대 체력의 8%만큼 보호막 부여</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -1871,7 +1877,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>아군 광신도 클래스는 자신 주변 반경 3에 다른 아군이 1명 이상 있으면 주는 회복량과 보호막량이 20% 증가</t>
+          <t xml:space="preserve">광신도 계열 아군은 주변 반경 3 안에 다른 아군이 1명 이상 있으면 주는 회복량과 보호막량이 20% 증가</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -1921,7 +1927,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신의 최대 체력의 2%만큼 회복</t>
+          <t xml:space="preserve">마법사 계열 아군이 액티브 스킬 사용을 마치면 자신의 최대 체력의 2%만큼 회복</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -1946,7 +1952,8 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스가 적을 처치하면 4초 동안 공격력이 10% 증가. 다시 발동하면 지속시간만 갱신</t>
+          <t xml:space="preserve">궁수 계열 아군이 적을 처치하면 4초 동안 공격력이 10% 증가
+중첩되지 않으며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -1971,7 +1978,8 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 5초 동안 받는 피해가 20% 감소. 다시 발동하면 지속시간만 갱신</t>
+          <t xml:space="preserve">전사 계열 아군이 액티브 스킬 사용을 마치면 5초 동안 받는 피해가 20% 감소
+중첩되지 않으며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -1996,7 +2004,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>아군 검사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 5의 가까운 적 최대 2명에게 각각 공격력의 75%에 해당하는 추가 물리 피해</t>
+          <t xml:space="preserve">검사 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 5 안의 가까운 적 최대 2명에게 각각 공격력의 75%만큼 추가 물리 피해를 줌</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2021,7 +2029,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>광전사는 체력이 60% 이하이면 받는 회복량과 보호막량이 50% 증가</t>
+          <t xml:space="preserve">광전사는 체력이 60% 이하일 때 받는 회복량과 보호막량이 50% 증가</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2046,7 +2054,8 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>저격수의 체력이 처음 40% 이하가 되면 자신의 최대 체력의 40%만큼 보호막 획득. 유닛마다 1회 발동</t>
+          <t xml:space="preserve">저격수의 체력이 처음 40% 이하로 떨어지면 자신의 최대 체력의 40%만큼 보호막 획득
+유닛당 1회 발동</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -2071,7 +2080,8 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>아군 1티어 유닛이 처음 액티브 스킬 사용을 시작하면 20초 동안 공격속도가 40% 증가. 유닛마다 1회 발동</t>
+          <t xml:space="preserve">아군 1티어 유닛이 첫 액티브 스킬을 사용하기 시작하면 20초 동안 공격속도가 40% 증가
+유닛당 1회 발동</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2096,7 +2106,8 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스는 체력이 50% 이하이면 공격속도가 75% 증가. 체력과 관계없이 받는 피해가 20% 증가</t>
+          <t xml:space="preserve">전사 계열 아군은 체력이 50% 이하일 때 공격속도가 75% 증가
+받는 피해는 항상 20% 증가</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2121,7 +2132,9 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>아군 검사 클래스가 액티브 스킬 사용을 완료하면 5초 동안 공격속도가 60% 증가. 다시 발동하면 지속시간만 갱신. 받는 회복량과 보호막량은 항상 30% 감소</t>
+          <t xml:space="preserve">검사 계열 아군이 액티브 스킬 사용을 마치면 5초 동안 공격속도가 60% 증가
+중첩되지 않으며 재발동 시 지속시간 갱신
+받는 회복량과 보호막량은 항상 30% 감소</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2146,7 +2159,8 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 16의 가까운 적 최대 4명에게 각각 공격력의 100%에 해당하는 물리 피해를 주는 추가 투사체 발사. 공격력은 항상 10% 감소</t>
+          <t xml:space="preserve">궁수 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 16 안의 가까운 적 최대 4명에게 추가 투사체를 발사해 각각 공격력의 100%만큼 물리 피해를 줌
+공격력은 항상 10% 감소</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2171,7 +2185,8 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>아군 광신도 클래스가 6초마다 자신 주변 반경 3의 다른 아군 최대 3명의 체력을 각각 자신의 최대 체력의 15%만큼 회복. 자신의 최대 체력은 20% 감소</t>
+          <t xml:space="preserve">광신도 계열 아군이 6초마다 주변 반경 3 안의 다른 아군 최대 3명을 자신의 최대 체력의 15%만큼 각각 회복
+자신의 최대 체력은 20% 감소</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -2196,7 +2211,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>아군 유닛은 6초마다 자신의 체력이 50% 이하이면 최대 체력의 2%만큼 회복</t>
+          <t xml:space="preserve">아군 유닛이 6초마다 체력이 50% 이하인 경우 자신의 최대 체력의 2%만큼 회복</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -2221,7 +2236,8 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>아군 검사 클래스가 적을 처치하면 3초 동안 이동속도가 12% 증가. 다시 발동하면 지속시간 갱신</t>
+          <t xml:space="preserve">검사 계열 아군이 적을 처치하면 3초 동안 이동속도가 12% 증가
+재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -2246,7 +2262,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>장궁수가 액티브 스킬 사용을 완료하면 자신 주변 반경 6의 적 최대 2명을 0.7초 동안 속박</t>
+          <t xml:space="preserve">장궁수가 액티브 스킬 사용을 마치면 주변 반경 6 안의 적 최대 2명을 0.7초 동안 속박</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2271,7 +2287,8 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>아군 검사 클래스가 피해를 줄 때마다 4초 동안 공격력이 3% 증가하며 최대 5회 중첩. 다시 발동하면 지속시간 갱신</t>
+          <t xml:space="preserve">검사 계열 아군이 피해를 줄 때마다 4초 동안 공격력이 3% 증가
+최대 5회 중첩되며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2296,7 +2313,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스는 자신 주변 반경 3에 다른 아군이 없으면 공격력이 18% 증가</t>
+          <t xml:space="preserve">궁수 계열 아군은 주변 반경 3 안에 다른 아군이 없으면 공격력이 18% 증가</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2346,7 +2363,8 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>철갑전사가 피해를 받을 때마다 4초 동안 방어력이 5% 증가하며 최대 4회 중첩. 다시 발동하면 지속시간 갱신</t>
+          <t xml:space="preserve">철갑전사가 피해를 받을 때마다 4초 동안 방어력이 5% 증가
+최대 4회 중첩되며 재발동 시 지속시간 갱신</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2371,7 +2389,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 2.5의 적 최대 3명을 0.4초 동안 기절시킴</t>
+          <t xml:space="preserve">전사 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 2.5 안의 적 최대 3명을 0.4초 동안 기절시킴</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2396,7 +2414,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>아군 마법사 클래스가 액티브 스킬 사용을 완료하면 자신 주변 반경 5의 적 최대 2명을 1초 동안 침묵시킴</t>
+          <t xml:space="preserve">마법사 계열 아군이 액티브 스킬 사용을 마치면 주변 반경 5 안의 적 최대 2명을 1초 동안 침묵시킴</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2421,7 +2439,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>빙결술사가 7초마다 자신 주변 반경 5의 적 최대 2명을 0.6초 동안 동결시킴</t>
+          <t xml:space="preserve">빙결술사가 7초마다 주변 반경 5 안의 적 최대 2명을 0.6초 동안 동결시킴</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2446,7 +2464,9 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>아군 전사 클래스가 피해를 줄 때마다 공격력이 5% 증가하며 최대 10회 중첩. 유닛이 유지되는 동안 지속되며 받는 피해가 25% 증가</t>
+          <t xml:space="preserve">전사 계열 아군이 피해를 줄 때마다 공격력이 5% 증가
+최대 10회 중첩되며 해당 유닛이 사라질 때까지 유지
+받는 피해는 항상 25% 증가</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2471,7 +2491,8 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>아군 궁수 클래스가 적을 처치하면 처치 위치 주변 반경 4의 적 최대 2명에게 공격력의 60%에 해당하는 물리 피해를 주는 투사체 발사. 공격력은 15% 감소</t>
+          <t xml:space="preserve">궁수 계열 아군이 적을 처치하면 처치한 적의 위치에서 반경 4 안의 적 최대 2명에게 투사체를 발사해 공격력의 60%만큼 물리 피해를 줌
+공격력은 15% 감소</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">

--- a/Assets/Data/Excel/Artifacts.xlsx
+++ b/Assets/Data/Excel/Artifacts.xlsx
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>흡혈의 송곳니</t>
+          <t xml:space="preserve">파쇄의 칼날</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">검사 계열 아군의 흡혈 비율이 3% 증가</t>
+          <t xml:space="preserve">검사 계열 아군의 방어력 무시 비율이 8% 증가</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>검성의 유산</t>
+          <t xml:space="preserve">검호의 휘장</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>아군 검사(1티어)의 기본 공격 배율이 50%, 흡혈 비율이 8% 증가</t>
+          <t xml:space="preserve">아군 검사(1티어)의 기본 공격 배율이 50%, 최대 체력이 20% 증가</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -1567,12 +1567,13 @@
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>피의 왕관</t>
+          <t xml:space="preserve">폭군의 왕관</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>아군 전체가 주는 피해 배율이 40%, 흡혈 비율이 10% 증가하고 받는 피해 배율이 30% 증가</t>
+          <t xml:space="preserve">아군 전체가 주는 피해 배율이 40%, 공격속도가 20% 증가
+받는 피해 배율이 30% 증가</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -1902,7 +1903,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>아군 1티어 유닛이 생성되면 자신의 최대 체력의 10%만큼 보호막 획득</t>
+          <t>아군 1티어 유닛이 처음 피해를 받으면 자신의 최대 체력의 10%만큼 보호막 획득</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -4449,7 +4450,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>LifeSteal</t>
+          <t xml:space="preserve">DefenseIgnore</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
@@ -4457,8 +4458,8 @@
           <t>Flat</t>
         </is>
       </c>
-      <c r="J24" s="0" t="n">
-        <v>0.03</v>
+      <c r="J24" s="0">
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
@@ -4899,16 +4900,16 @@
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>LifeSteal</t>
+          <t xml:space="preserve">MaxHp</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>0.08</v>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J33" s="0">
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -5699,16 +5700,16 @@
       </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>LifeSteal</t>
+          <t xml:space="preserve">AttackSpeed</t>
         </is>
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J49" s="0" t="n">
-        <v>0.1</v>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="J49" s="0">
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
@@ -7824,7 +7825,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Initialize</t>
+          <t>DamageTaken</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
